--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Río Breogán.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Río Breogán.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>42.3166</v>
+        <v>41.1465</v>
       </c>
       <c r="E2" t="n">
-        <v>57.0629</v>
+        <v>60.0838</v>
       </c>
       <c r="F2" t="n">
-        <v>-14.7465</v>
+        <v>-18.9376</v>
       </c>
       <c r="G2" t="n">
-        <v>8.6439</v>
+        <v>13.3187</v>
       </c>
       <c r="H2" t="n">
-        <v>23.2291</v>
+        <v>29.5189</v>
       </c>
       <c r="I2" t="n">
-        <v>-14.5848</v>
+        <v>-16.2002</v>
       </c>
       <c r="J2" t="n">
-        <v>39.7338</v>
+        <v>49.7259</v>
       </c>
       <c r="K2" t="n">
-        <v>34.199</v>
+        <v>42.8951</v>
       </c>
       <c r="L2" t="n">
-        <v>5.535400000000001</v>
+        <v>6.830499999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-31.0899</v>
+        <v>-36.4073</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.9702</v>
+        <v>-13.376</v>
       </c>
       <c r="O2" t="n">
-        <v>-20.1199</v>
+        <v>-23.0307</v>
       </c>
       <c r="P2" t="n">
-        <v>2.268400000000001</v>
+        <v>4.097599999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-36.2933</v>
+        <v>-44.3885</v>
       </c>
       <c r="R2" t="n">
-        <v>38.5617</v>
+        <v>48.4857</v>
       </c>
       <c r="S2" t="n">
-        <v>37.7808</v>
+        <v>35.7425</v>
       </c>
       <c r="T2" t="n">
-        <v>33.118</v>
+        <v>31.2927</v>
       </c>
       <c r="U2" t="n">
-        <v>4.6628</v>
+        <v>4.4493</v>
       </c>
       <c r="V2" t="n">
-        <v>-6.3765</v>
+        <v>-12.0112</v>
       </c>
       <c r="W2" t="n">
-        <v>20.5039</v>
+        <v>23.4534</v>
       </c>
       <c r="X2" t="n">
-        <v>-26.8807</v>
+        <v>-35.4651</v>
       </c>
     </row>
     <row r="3">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>32.9003</v>
+        <v>31.8642</v>
       </c>
       <c r="E3" t="n">
-        <v>38.6984</v>
+        <v>41.7051</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.798</v>
+        <v>-9.841199999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>7.361099999999999</v>
+        <v>5.258600000000003</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.9781</v>
+        <v>-14.4113</v>
       </c>
       <c r="I3" t="n">
-        <v>14.3391</v>
+        <v>19.6697</v>
       </c>
       <c r="J3" t="n">
-        <v>38.9744</v>
+        <v>44.675</v>
       </c>
       <c r="K3" t="n">
-        <v>8.375400000000001</v>
+        <v>5.1745</v>
       </c>
       <c r="L3" t="n">
-        <v>30.5991</v>
+        <v>39.5001</v>
       </c>
       <c r="M3" t="n">
-        <v>-31.6134</v>
+        <v>-39.4163</v>
       </c>
       <c r="N3" t="n">
-        <v>-15.3535</v>
+        <v>-19.5862</v>
       </c>
       <c r="O3" t="n">
-        <v>-16.2599</v>
+        <v>-19.8305</v>
       </c>
       <c r="P3" t="n">
-        <v>3.176000000000001</v>
+        <v>5.2358</v>
       </c>
       <c r="Q3" t="n">
-        <v>-49.9036</v>
+        <v>-60.5503</v>
       </c>
       <c r="R3" t="n">
-        <v>53.0791</v>
+        <v>65.7856</v>
       </c>
       <c r="S3" t="n">
-        <v>-19.9033</v>
+        <v>-25.1902</v>
       </c>
       <c r="T3" t="n">
-        <v>-9.442</v>
+        <v>-11.4021</v>
       </c>
       <c r="U3" t="n">
-        <v>-10.4612</v>
+        <v>-13.7881</v>
       </c>
       <c r="V3" t="n">
-        <v>42.2668</v>
+        <v>46.5604</v>
       </c>
       <c r="W3" t="n">
-        <v>59.069</v>
+        <v>68.9823</v>
       </c>
       <c r="X3" t="n">
-        <v>-16.8019</v>
+        <v>-22.4218</v>
       </c>
     </row>
     <row r="4">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>16.3927</v>
+        <v>21.7759</v>
       </c>
       <c r="E4" t="n">
-        <v>23.6586</v>
+        <v>28.1448</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.2655</v>
+        <v>-6.3688</v>
       </c>
       <c r="G4" t="n">
-        <v>-15.9749</v>
+        <v>-20.8218</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.3885</v>
+        <v>-3.3743</v>
       </c>
       <c r="I4" t="n">
-        <v>-12.5865</v>
+        <v>-17.4475</v>
       </c>
       <c r="J4" t="n">
-        <v>6.867699999999999</v>
+        <v>6.4955</v>
       </c>
       <c r="K4" t="n">
-        <v>9.6259</v>
+        <v>10.6618</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.7576</v>
+        <v>-4.1662</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.8431</v>
+        <v>-27.3174</v>
       </c>
       <c r="N4" t="n">
-        <v>-13.0148</v>
+        <v>-14.0362</v>
       </c>
       <c r="O4" t="n">
-        <v>-9.8287</v>
+        <v>-13.2812</v>
       </c>
       <c r="P4" t="n">
-        <v>21.7759</v>
+        <v>25.7225</v>
       </c>
       <c r="Q4" t="n">
-        <v>-15.8783</v>
+        <v>-20.7146</v>
       </c>
       <c r="R4" t="n">
-        <v>37.6541</v>
+        <v>46.437</v>
       </c>
       <c r="S4" t="n">
-        <v>13.5617</v>
+        <v>16.6495</v>
       </c>
       <c r="T4" t="n">
-        <v>18.1744</v>
+        <v>22.8811</v>
       </c>
       <c r="U4" t="n">
-        <v>-4.6126</v>
+        <v>-6.2317</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.9701</v>
+        <v>0.2254</v>
       </c>
       <c r="W4" t="n">
-        <v>14.4945</v>
+        <v>19.4825</v>
       </c>
       <c r="X4" t="n">
-        <v>-17.4644</v>
+        <v>-19.257</v>
       </c>
     </row>
     <row r="5">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>9.704599999999999</v>
+        <v>9.807799999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>26.2977</v>
+        <v>29.1228</v>
       </c>
       <c r="F5" t="n">
-        <v>-16.5929</v>
+        <v>-19.3145</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2607</v>
+        <v>-3.402000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4894</v>
+        <v>4.071</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.7501</v>
+        <v>-7.473100000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>27.653</v>
+        <v>29.1501</v>
       </c>
       <c r="K5" t="n">
-        <v>19.0326</v>
+        <v>20.3994</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6205</v>
+        <v>8.750400000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-30.9138</v>
+        <v>-32.5522</v>
       </c>
       <c r="N5" t="n">
-        <v>-15.5433</v>
+        <v>-16.3285</v>
       </c>
       <c r="O5" t="n">
-        <v>-15.3701</v>
+        <v>-16.224</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9072999999999998</v>
+        <v>-0.2275999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.5713</v>
+        <v>-33.6897</v>
       </c>
       <c r="R5" t="n">
-        <v>32.6641</v>
+        <v>33.4622</v>
       </c>
       <c r="S5" t="n">
-        <v>22.9931</v>
+        <v>24.5502</v>
       </c>
       <c r="T5" t="n">
-        <v>21.6099</v>
+        <v>22.9671</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3832</v>
+        <v>1.5834</v>
       </c>
       <c r="V5" t="n">
-        <v>-9.120900000000001</v>
+        <v>-11.1125</v>
       </c>
       <c r="W5" t="n">
-        <v>10.6057</v>
+        <v>10.6952</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.7267</v>
+        <v>-21.8077</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DREZNJAK</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0936</v>
+        <v>6.8855</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1702</v>
+        <v>11.859</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9234</v>
+        <v>-4.973600000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7195</v>
+        <v>-38.2657</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9465</v>
+        <v>-18.5174</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6659</v>
+        <v>-19.748</v>
       </c>
       <c r="J6" t="n">
-        <v>0.519</v>
+        <v>9.872900000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1.42</v>
+        <v>3.7662</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.901</v>
+        <v>6.1065</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2384</v>
+        <v>-48.1385</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4735</v>
+        <v>-22.2835</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7649</v>
+        <v>-25.8548</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>40.7461</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-22.0806</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1342</v>
+        <v>62.8264</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3741</v>
+        <v>14.0653</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2843</v>
+        <v>7.1646</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6584</v>
+        <v>6.900399999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-9.6601</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>16.9019</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1607</v>
+        <v>-26.5618</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>I. CRUZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2627</v>
+        <v>-0.7548</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4527000000000001</v>
+        <v>0.6032000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8097</v>
+        <v>-1.358</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8333</v>
+        <v>0.332</v>
       </c>
       <c r="H7" t="n">
-        <v>4.099699999999999</v>
+        <v>-0.8507</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2665000000000002</v>
+        <v>1.1825</v>
       </c>
       <c r="J7" t="n">
-        <v>8.883900000000001</v>
+        <v>1.737</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8349</v>
+        <v>0.0689</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0492</v>
+        <v>1.668</v>
       </c>
       <c r="M7" t="n">
-        <v>-5.050800000000001</v>
+        <v>-1.405</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.735</v>
+        <v>-0.9196</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.3158</v>
+        <v>-0.4855</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0416</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-8.1661</v>
+        <v>-1.3658</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1244</v>
+        <v>0.6828</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1656000000000002</v>
+        <v>-0.1370999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.496</v>
+        <v>0.232</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3304</v>
+        <v>-0.3692</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.8885</v>
+        <v>-0.2667</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6746</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.2139</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>D. DREZNJAK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.630299999999998</v>
+        <v>-1.0864</v>
       </c>
       <c r="E8" t="n">
-        <v>2.898700000000001</v>
+        <v>-0.1884</v>
       </c>
       <c r="F8" t="n">
-        <v>-7.529000000000001</v>
+        <v>-0.898</v>
       </c>
       <c r="G8" t="n">
-        <v>-37.7083</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-17.4237</v>
+        <v>0.9532</v>
       </c>
       <c r="I8" t="n">
-        <v>-20.2848</v>
+        <v>-1.6654</v>
       </c>
       <c r="J8" t="n">
-        <v>3.294199999999999</v>
+        <v>0.5044</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2468</v>
+        <v>1.4134</v>
       </c>
       <c r="L8" t="n">
-        <v>2.0473</v>
+        <v>-0.909</v>
       </c>
       <c r="M8" t="n">
-        <v>-41.0024</v>
+        <v>-1.2166</v>
       </c>
       <c r="N8" t="n">
-        <v>-18.6708</v>
+        <v>-0.4603</v>
       </c>
       <c r="O8" t="n">
-        <v>-22.3319</v>
+        <v>-0.7563</v>
       </c>
       <c r="P8" t="n">
-        <v>31.3028</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-18.6004</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>49.9031</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>12.2653</v>
+        <v>-0.3742</v>
       </c>
       <c r="T8" t="n">
-        <v>7.727900000000001</v>
+        <v>0.2876</v>
       </c>
       <c r="U8" t="n">
-        <v>4.5372</v>
+        <v>-0.6618000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-10.4901</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>10.4769</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-20.9669</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.3584</v>
+        <v>-3.203399999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2903</v>
+        <v>0.5452000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0681</v>
+        <v>-3.7486</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8073</v>
+        <v>1.465500000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5354</v>
+        <v>2.7356</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2719</v>
+        <v>-1.2699</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.901</v>
+        <v>9.4412</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>5.7108</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.901</v>
+        <v>3.7302</v>
       </c>
       <c r="M9" t="n">
-        <v>0.09370000000000001</v>
+        <v>-7.9758</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5354</v>
+        <v>-2.9753</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>-5.0003</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-9.3331</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>7.511699999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5511</v>
+        <v>2.513</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.121</v>
+        <v>1.8986</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4301</v>
+        <v>0.6145</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.1853</v>
+        <v>-5.3609</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-1.4614</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1853</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.111700000000002</v>
+        <v>-4.2409</v>
       </c>
       <c r="E10" t="n">
-        <v>19.7472</v>
+        <v>14.7949</v>
       </c>
       <c r="F10" t="n">
-        <v>-25.8586</v>
+        <v>-19.0357</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.097900000000002</v>
+        <v>-15.8951</v>
       </c>
       <c r="H10" t="n">
-        <v>-12.5717</v>
+        <v>-12.1578</v>
       </c>
       <c r="I10" t="n">
-        <v>7.4739</v>
+        <v>-3.7375</v>
       </c>
       <c r="J10" t="n">
-        <v>37.9447</v>
+        <v>30.2178</v>
       </c>
       <c r="K10" t="n">
-        <v>6.1289</v>
+        <v>10.7428</v>
       </c>
       <c r="L10" t="n">
-        <v>31.8159</v>
+        <v>19.4747</v>
       </c>
       <c r="M10" t="n">
-        <v>-43.043</v>
+        <v>-46.1129</v>
       </c>
       <c r="N10" t="n">
-        <v>-18.7008</v>
+        <v>-22.9009</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.3419</v>
+        <v>-23.2121</v>
       </c>
       <c r="P10" t="n">
-        <v>11.7955</v>
+        <v>-2.731299999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-30.3956</v>
+        <v>-51.6721</v>
       </c>
       <c r="R10" t="n">
-        <v>42.1912</v>
+        <v>48.9411</v>
       </c>
       <c r="S10" t="n">
-        <v>-10.6747</v>
+        <v>-10.5822</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8532000000000003</v>
+        <v>-9.3653</v>
       </c>
       <c r="U10" t="n">
-        <v>-11.528</v>
+        <v>-1.2166</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1341</v>
+        <v>24.968</v>
       </c>
       <c r="W10" t="n">
-        <v>11.3447</v>
+        <v>45.6148</v>
       </c>
       <c r="X10" t="n">
-        <v>-13.479</v>
+        <v>-20.6469</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.379399999999999</v>
+        <v>-5.398</v>
       </c>
       <c r="E11" t="n">
-        <v>10.6651</v>
+        <v>21.8877</v>
       </c>
       <c r="F11" t="n">
-        <v>-18.0445</v>
+        <v>-27.2853</v>
       </c>
       <c r="G11" t="n">
-        <v>-22.1947</v>
+        <v>-6.754400000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-11.3858</v>
+        <v>-15.6383</v>
       </c>
       <c r="I11" t="n">
-        <v>-10.8095</v>
+        <v>8.883199999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>18.322</v>
+        <v>46.6252</v>
       </c>
       <c r="K11" t="n">
-        <v>6.8151</v>
+        <v>11.2123</v>
       </c>
       <c r="L11" t="n">
-        <v>11.507</v>
+        <v>35.4135</v>
       </c>
       <c r="M11" t="n">
-        <v>-40.5164</v>
+        <v>-53.3801</v>
       </c>
       <c r="N11" t="n">
-        <v>-18.2003</v>
+        <v>-26.85</v>
       </c>
       <c r="O11" t="n">
-        <v>-22.316</v>
+        <v>-26.5303</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6804000000000001</v>
+        <v>17.528</v>
       </c>
       <c r="Q11" t="n">
-        <v>-42.1909</v>
+        <v>-36.4212</v>
       </c>
       <c r="R11" t="n">
-        <v>41.5106</v>
+        <v>53.9492</v>
       </c>
       <c r="S11" t="n">
-        <v>-9.063000000000001</v>
+        <v>-14.997</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.7906</v>
+        <v>-3.0392</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2727</v>
+        <v>-11.9577</v>
       </c>
       <c r="V11" t="n">
-        <v>24.559</v>
+        <v>-1.173</v>
       </c>
       <c r="W11" t="n">
-        <v>42.3249</v>
+        <v>14.7231</v>
       </c>
       <c r="X11" t="n">
-        <v>-17.7659</v>
+        <v>-15.896</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.9697</v>
+        <v>-7.907400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.933000000000001</v>
+        <v>5.701000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.0366</v>
+        <v>-13.6087</v>
       </c>
       <c r="G12" t="n">
-        <v>33.8124</v>
+        <v>-4.3598</v>
       </c>
       <c r="H12" t="n">
-        <v>21.6129</v>
+        <v>-0.9623999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>12.1996</v>
+        <v>-3.3975</v>
       </c>
       <c r="J12" t="n">
-        <v>62.9615</v>
+        <v>17.7756</v>
       </c>
       <c r="K12" t="n">
-        <v>36.0476</v>
+        <v>12.4214</v>
       </c>
       <c r="L12" t="n">
-        <v>26.9138</v>
+        <v>5.3544</v>
       </c>
       <c r="M12" t="n">
-        <v>-29.149</v>
+        <v>-22.1353</v>
       </c>
       <c r="N12" t="n">
-        <v>-14.4354</v>
+        <v>-13.3834</v>
       </c>
       <c r="O12" t="n">
-        <v>-14.7143</v>
+        <v>-8.751899999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-43.3252</v>
+        <v>4.5527</v>
       </c>
       <c r="Q12" t="n">
-        <v>-81.8867</v>
+        <v>-25.7227</v>
       </c>
       <c r="R12" t="n">
-        <v>38.5617</v>
+        <v>30.2752</v>
       </c>
       <c r="S12" t="n">
-        <v>-7.382000000000001</v>
+        <v>4.872100000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3021999999999998</v>
+        <v>8.1411</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.08</v>
+        <v>-3.2691</v>
       </c>
       <c r="V12" t="n">
-        <v>7.9253</v>
+        <v>-12.9724</v>
       </c>
       <c r="W12" t="n">
-        <v>16.2945</v>
+        <v>5.5072</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.369</v>
+        <v>-18.4794</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.5272</v>
+        <v>-11.1928</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1943</v>
+        <v>-6.090899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.3328</v>
+        <v>-5.102</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.1214</v>
+        <v>37.5372</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.819299999999999</v>
+        <v>17.0981</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.3018</v>
+        <v>20.4395</v>
       </c>
       <c r="J13" t="n">
-        <v>10.0664</v>
+        <v>71.63590000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>6.8223</v>
+        <v>34.9571</v>
       </c>
       <c r="L13" t="n">
-        <v>3.244</v>
+        <v>36.6795</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.1874</v>
+        <v>-34.0986</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.6419</v>
+        <v>-17.8589</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.5457</v>
+        <v>-16.2398</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6805000000000001</v>
+        <v>-49.1684</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.7346</v>
+        <v>-97.1985</v>
       </c>
       <c r="R13" t="n">
-        <v>20.415</v>
+        <v>48.0305</v>
       </c>
       <c r="S13" t="n">
-        <v>3.997</v>
+        <v>-13.1915</v>
       </c>
       <c r="T13" t="n">
-        <v>5.5168</v>
+        <v>-2.8203</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5196</v>
+        <v>-10.3706</v>
       </c>
       <c r="V13" t="n">
-        <v>-12.0836</v>
+        <v>13.6298</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9571</v>
+        <v>22.2927</v>
       </c>
       <c r="X13" t="n">
-        <v>-15.0406</v>
+        <v>-8.662799999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-54.2151</v>
+        <v>-14.316</v>
       </c>
       <c r="E14" t="n">
-        <v>-31.6534</v>
+        <v>-4.7926</v>
       </c>
       <c r="F14" t="n">
-        <v>-22.5619</v>
+        <v>-9.523399999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-49.5886</v>
+        <v>-3.1783</v>
       </c>
       <c r="H14" t="n">
-        <v>-15.629</v>
+        <v>-2.1229</v>
       </c>
       <c r="I14" t="n">
-        <v>-33.9599</v>
+        <v>-1.0553</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8269</v>
+        <v>0.9037000000000003</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9091</v>
+        <v>-0.1972</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.736100000000001</v>
+        <v>1.1007</v>
       </c>
       <c r="M14" t="n">
-        <v>-45.7617</v>
+        <v>-4.0818</v>
       </c>
       <c r="N14" t="n">
-        <v>-19.5382</v>
+        <v>-1.9258</v>
       </c>
       <c r="O14" t="n">
-        <v>-26.2236</v>
+        <v>-2.156</v>
       </c>
       <c r="P14" t="n">
-        <v>20.8685</v>
+        <v>-4.3251</v>
       </c>
       <c r="Q14" t="n">
-        <v>-25.4053</v>
+        <v>-5.9184</v>
       </c>
       <c r="R14" t="n">
-        <v>46.2738</v>
+        <v>1.5935</v>
       </c>
       <c r="S14" t="n">
-        <v>-16.6316</v>
+        <v>-2.0303</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.6674</v>
+        <v>0.2222</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.9642</v>
+        <v>-2.2526</v>
       </c>
       <c r="V14" t="n">
-        <v>-8.8634</v>
+        <v>-4.7823</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2463</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-12.1095</v>
+        <v>-4.7823</v>
       </c>
     </row>
     <row r="15">
@@ -1576,148 +1576,226 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>-62.5863</v>
+        <v>-57.6832</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.4938</v>
+        <v>-23.674</v>
       </c>
       <c r="F15" t="n">
-        <v>-37.0924</v>
+        <v>-34.0094</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.916499999999999</v>
+        <v>8.856399999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-14.5431</v>
+        <v>-15.8525</v>
       </c>
       <c r="I15" t="n">
-        <v>11.6269</v>
+        <v>24.7084</v>
       </c>
       <c r="J15" t="n">
-        <v>39.6356</v>
+        <v>55.916</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2368</v>
+        <v>6.574100000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>35.3981</v>
+        <v>49.34220000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-42.5517</v>
+        <v>-47.0597</v>
       </c>
       <c r="N15" t="n">
-        <v>-18.7803</v>
+        <v>-22.4259</v>
       </c>
       <c r="O15" t="n">
-        <v>-23.7719</v>
+        <v>-24.6333</v>
       </c>
       <c r="P15" t="n">
-        <v>-22.6834</v>
+        <v>-25.2673</v>
       </c>
       <c r="Q15" t="n">
-        <v>-68.9573</v>
+        <v>-81.9474</v>
       </c>
       <c r="R15" t="n">
-        <v>46.2738</v>
+        <v>56.6803</v>
       </c>
       <c r="S15" t="n">
-        <v>-24.234</v>
+        <v>-29.0241</v>
       </c>
       <c r="T15" t="n">
-        <v>-9.959099999999999</v>
+        <v>-12.2222</v>
       </c>
       <c r="U15" t="n">
-        <v>-14.2751</v>
+        <v>-16.8014</v>
       </c>
       <c r="V15" t="n">
-        <v>-12.7523</v>
+        <v>-12.2486</v>
       </c>
       <c r="W15" t="n">
-        <v>13.7871</v>
+        <v>14.5798</v>
       </c>
       <c r="X15" t="n">
-        <v>-26.5396</v>
+        <v>-26.8286</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>A. KURUCS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Río Breogán</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-62.4041</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-42.088</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-20.3164</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-54.9498</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-21.3147</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-33.6351</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-3.195500000000001</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.0517</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-6.247199999999999</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-51.7541</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-24.3666</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-27.3876</v>
+      </c>
+      <c r="P16" t="n">
+        <v>23.9013</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-33.6895</v>
+      </c>
+      <c r="R16" t="n">
+        <v>57.5909</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-21.103</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-8.414400000000001</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-12.6887</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-10.2524</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.2121</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-13.4642</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>--- TOTAL ---</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Río Breogán</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>28</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-63.82020000000001</v>
-      </c>
-      <c r="E16" t="n">
-        <v>113.8409</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-177.6599</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-89.73910000000002</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-30.897</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-58.8422</v>
-      </c>
-      <c r="J16" t="n">
-        <v>290.1283</v>
-      </c>
-      <c r="K16" t="n">
-        <v>143.6944</v>
-      </c>
-      <c r="L16" t="n">
-        <v>146.4346</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-379.8673</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-174.5934</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-205.2755</v>
-      </c>
-      <c r="P16" t="n">
-        <v>20.415</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-434.3859</v>
-      </c>
-      <c r="R16" t="n">
-        <v>454.8005</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.618499999999994</v>
-      </c>
-      <c r="T16" t="n">
-        <v>53.50620000000001</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-51.8883</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3.886299999999997</v>
-      </c>
-      <c r="W16" t="n">
-        <v>204.5907</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-200.7041</v>
+      <c r="C17" t="n">
+        <v>34</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-56.70709999999998</v>
+      </c>
+      <c r="E17" t="n">
+        <v>137.6136</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-194.3212</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-81.57069999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-50.8255</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-30.74619999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>371.4807000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>168.8523</v>
+      </c>
+      <c r="L17" t="n">
+        <v>202.6283</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-453.0516</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-219.6771</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-233.3743</v>
+      </c>
+      <c r="P17" t="n">
+        <v>37.56030000000001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-525.8306</v>
+      </c>
+      <c r="R17" t="n">
+        <v>563.3903</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-18.23700000000001</v>
+      </c>
+      <c r="T17" t="n">
+        <v>47.8235</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-66.0599</v>
+      </c>
+      <c r="V17" t="n">
+        <v>5.543499999999993</v>
+      </c>
+      <c r="W17" t="n">
+        <v>244.1414</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-238.5976</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Río Breogán.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate_individual/AGG_IND_Río Breogán.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>34</v>
       </c>
       <c r="D2" t="n">
-        <v>41.1465</v>
+        <v>52.782</v>
       </c>
       <c r="E2" t="n">
-        <v>60.0838</v>
+        <v>55.6128</v>
       </c>
       <c r="F2" t="n">
-        <v>-18.9376</v>
+        <v>-2.831099999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>13.3187</v>
+        <v>5.258600000000003</v>
       </c>
       <c r="H2" t="n">
-        <v>29.5189</v>
+        <v>-14.4113</v>
       </c>
       <c r="I2" t="n">
-        <v>-16.2002</v>
+        <v>19.6697</v>
       </c>
       <c r="J2" t="n">
-        <v>49.7259</v>
+        <v>44.675</v>
       </c>
       <c r="K2" t="n">
-        <v>42.8951</v>
+        <v>5.1745</v>
       </c>
       <c r="L2" t="n">
-        <v>6.830499999999999</v>
+        <v>39.5001</v>
       </c>
       <c r="M2" t="n">
-        <v>-36.4073</v>
+        <v>-39.4163</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.376</v>
+        <v>-19.5862</v>
       </c>
       <c r="O2" t="n">
-        <v>-23.0307</v>
+        <v>-19.8305</v>
       </c>
       <c r="P2" t="n">
-        <v>4.097599999999999</v>
+        <v>5.2358</v>
       </c>
       <c r="Q2" t="n">
-        <v>-44.3885</v>
+        <v>-60.5503</v>
       </c>
       <c r="R2" t="n">
-        <v>48.4857</v>
+        <v>65.7856</v>
       </c>
       <c r="S2" t="n">
-        <v>35.7425</v>
+        <v>-4.2726</v>
       </c>
       <c r="T2" t="n">
-        <v>31.2927</v>
+        <v>2.5053</v>
       </c>
       <c r="U2" t="n">
-        <v>4.4493</v>
+        <v>-6.7782</v>
       </c>
       <c r="V2" t="n">
-        <v>-12.0112</v>
+        <v>46.5604</v>
       </c>
       <c r="W2" t="n">
-        <v>23.4534</v>
+        <v>68.9823</v>
       </c>
       <c r="X2" t="n">
-        <v>-35.4651</v>
+        <v>-22.4218</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>31.8642</v>
+        <v>18.4191</v>
       </c>
       <c r="E3" t="n">
-        <v>41.7051</v>
+        <v>41.6413</v>
       </c>
       <c r="F3" t="n">
-        <v>-9.841199999999999</v>
+        <v>-23.2226</v>
       </c>
       <c r="G3" t="n">
-        <v>5.258600000000003</v>
+        <v>13.3187</v>
       </c>
       <c r="H3" t="n">
-        <v>-14.4113</v>
+        <v>29.5189</v>
       </c>
       <c r="I3" t="n">
-        <v>19.6697</v>
+        <v>-16.2002</v>
       </c>
       <c r="J3" t="n">
-        <v>44.675</v>
+        <v>49.7259</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1745</v>
+        <v>42.8951</v>
       </c>
       <c r="L3" t="n">
-        <v>39.5001</v>
+        <v>6.830499999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>-39.4163</v>
+        <v>-36.4073</v>
       </c>
       <c r="N3" t="n">
-        <v>-19.5862</v>
+        <v>-13.376</v>
       </c>
       <c r="O3" t="n">
-        <v>-19.8305</v>
+        <v>-23.0307</v>
       </c>
       <c r="P3" t="n">
-        <v>5.2358</v>
+        <v>4.097599999999999</v>
       </c>
       <c r="Q3" t="n">
-        <v>-60.5503</v>
+        <v>-44.3885</v>
       </c>
       <c r="R3" t="n">
-        <v>65.7856</v>
+        <v>48.4857</v>
       </c>
       <c r="S3" t="n">
-        <v>-25.1902</v>
+        <v>13.0143</v>
       </c>
       <c r="T3" t="n">
-        <v>-11.4021</v>
+        <v>12.8502</v>
       </c>
       <c r="U3" t="n">
-        <v>-13.7881</v>
+        <v>0.1641</v>
       </c>
       <c r="V3" t="n">
-        <v>46.5604</v>
+        <v>-12.0112</v>
       </c>
       <c r="W3" t="n">
-        <v>68.9823</v>
+        <v>23.4534</v>
       </c>
       <c r="X3" t="n">
-        <v>-22.4218</v>
+        <v>-35.4651</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>21.7759</v>
+        <v>12.0351</v>
       </c>
       <c r="E4" t="n">
-        <v>28.1448</v>
+        <v>16.2587</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.3688</v>
+        <v>-4.223799999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-20.8218</v>
@@ -766,13 +766,13 @@
         <v>46.437</v>
       </c>
       <c r="S4" t="n">
-        <v>16.6495</v>
+        <v>6.9083</v>
       </c>
       <c r="T4" t="n">
-        <v>22.8811</v>
+        <v>10.9954</v>
       </c>
       <c r="U4" t="n">
-        <v>-6.2317</v>
+        <v>-4.0863</v>
       </c>
       <c r="V4" t="n">
         <v>0.2254</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>9.807799999999999</v>
+        <v>6.192900000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>29.1228</v>
+        <v>27.3433</v>
       </c>
       <c r="F5" t="n">
-        <v>-19.3145</v>
+        <v>-21.15</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.402000000000001</v>
+        <v>-6.754400000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.071</v>
+        <v>-15.6383</v>
       </c>
       <c r="I5" t="n">
-        <v>-7.473100000000001</v>
+        <v>8.883199999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>29.1501</v>
+        <v>46.6252</v>
       </c>
       <c r="K5" t="n">
-        <v>20.3994</v>
+        <v>11.2123</v>
       </c>
       <c r="L5" t="n">
-        <v>8.750400000000001</v>
+        <v>35.4135</v>
       </c>
       <c r="M5" t="n">
-        <v>-32.5522</v>
+        <v>-53.3801</v>
       </c>
       <c r="N5" t="n">
-        <v>-16.3285</v>
+        <v>-26.85</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.224</v>
+        <v>-26.5303</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2275999999999999</v>
+        <v>17.528</v>
       </c>
       <c r="Q5" t="n">
-        <v>-33.6897</v>
+        <v>-36.4212</v>
       </c>
       <c r="R5" t="n">
-        <v>33.4622</v>
+        <v>53.9492</v>
       </c>
       <c r="S5" t="n">
-        <v>24.5502</v>
+        <v>-3.4061</v>
       </c>
       <c r="T5" t="n">
-        <v>22.9671</v>
+        <v>2.4163</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5834</v>
+        <v>-5.822500000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-11.1125</v>
+        <v>-1.173</v>
       </c>
       <c r="W5" t="n">
-        <v>10.6952</v>
+        <v>14.7231</v>
       </c>
       <c r="X5" t="n">
-        <v>-21.8077</v>
+        <v>-15.896</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>6.8855</v>
+        <v>4.257299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>11.859</v>
+        <v>23.8736</v>
       </c>
       <c r="F6" t="n">
-        <v>-4.973600000000001</v>
+        <v>-19.6163</v>
       </c>
       <c r="G6" t="n">
-        <v>-38.2657</v>
+        <v>-15.8951</v>
       </c>
       <c r="H6" t="n">
-        <v>-18.5174</v>
+        <v>-12.1578</v>
       </c>
       <c r="I6" t="n">
-        <v>-19.748</v>
+        <v>-3.7375</v>
       </c>
       <c r="J6" t="n">
-        <v>9.872900000000001</v>
+        <v>30.2178</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7662</v>
+        <v>10.7428</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1065</v>
+        <v>19.4747</v>
       </c>
       <c r="M6" t="n">
-        <v>-48.1385</v>
+        <v>-46.1129</v>
       </c>
       <c r="N6" t="n">
-        <v>-22.2835</v>
+        <v>-22.9009</v>
       </c>
       <c r="O6" t="n">
-        <v>-25.8548</v>
+        <v>-23.2121</v>
       </c>
       <c r="P6" t="n">
-        <v>40.7461</v>
+        <v>-2.731299999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>-22.0806</v>
+        <v>-51.6721</v>
       </c>
       <c r="R6" t="n">
-        <v>62.8264</v>
+        <v>48.9411</v>
       </c>
       <c r="S6" t="n">
-        <v>14.0653</v>
+        <v>-2.0838</v>
       </c>
       <c r="T6" t="n">
-        <v>7.1646</v>
+        <v>-0.2867000000000003</v>
       </c>
       <c r="U6" t="n">
-        <v>6.900399999999999</v>
+        <v>-1.7976</v>
       </c>
       <c r="V6" t="n">
-        <v>-9.6601</v>
+        <v>24.968</v>
       </c>
       <c r="W6" t="n">
-        <v>16.9019</v>
+        <v>45.6148</v>
       </c>
       <c r="X6" t="n">
-        <v>-26.5618</v>
+        <v>-20.6469</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CRUZ</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7548</v>
+        <v>1.879899999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6032000000000001</v>
+        <v>13.0511</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.358</v>
+        <v>-11.171</v>
       </c>
       <c r="G7" t="n">
-        <v>0.332</v>
+        <v>-38.2657</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8507</v>
+        <v>-18.5174</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1825</v>
+        <v>-19.748</v>
       </c>
       <c r="J7" t="n">
-        <v>1.737</v>
+        <v>9.872900000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0689</v>
+        <v>3.7662</v>
       </c>
       <c r="L7" t="n">
-        <v>1.668</v>
+        <v>6.1065</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.405</v>
+        <v>-48.1385</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9196</v>
+        <v>-22.2835</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4855</v>
+        <v>-25.8548</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6829</v>
+        <v>40.7461</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3658</v>
+        <v>-22.0806</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6828</v>
+        <v>62.8264</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1370999999999999</v>
+        <v>9.0595</v>
       </c>
       <c r="T7" t="n">
-        <v>0.232</v>
+        <v>8.3567</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3692</v>
+        <v>0.7027999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2667</v>
+        <v>-9.6601</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>16.9019</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2667</v>
+        <v>-26.5618</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. DREZNJAK</t>
+          <t>D. MAVRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0864</v>
+        <v>0.6227000000000014</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1884</v>
+        <v>-0.279599999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.898</v>
+        <v>0.9021000000000008</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7122000000000001</v>
+        <v>37.5372</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9532</v>
+        <v>17.0981</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6654</v>
+        <v>20.4395</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5044</v>
+        <v>71.63590000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4134</v>
+        <v>34.9571</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.909</v>
+        <v>36.6795</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.2166</v>
+        <v>-34.0986</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4603</v>
+        <v>-17.8589</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7563</v>
+        <v>-16.2398</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-49.1684</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1382</v>
+        <v>-97.1985</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1382</v>
+        <v>48.0305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3742</v>
+        <v>-1.376300000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2876</v>
+        <v>2.9903</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-4.3667</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>13.6298</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1578</v>
+        <v>22.2927</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1578</v>
+        <v>-8.662799999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>I. CRUZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.203399999999999</v>
+        <v>-0.4401</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5452000000000001</v>
+        <v>0.6032</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7486</v>
+        <v>-1.0433</v>
       </c>
       <c r="G9" t="n">
-        <v>1.465500000000001</v>
+        <v>0.332</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7356</v>
+        <v>-0.8507</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2699</v>
+        <v>1.1825</v>
       </c>
       <c r="J9" t="n">
-        <v>9.4412</v>
+        <v>1.737</v>
       </c>
       <c r="K9" t="n">
-        <v>5.7108</v>
+        <v>0.0689</v>
       </c>
       <c r="L9" t="n">
-        <v>3.7302</v>
+        <v>1.668</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.9758</v>
+        <v>-1.405</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.9753</v>
+        <v>-0.9196</v>
       </c>
       <c r="O9" t="n">
-        <v>-5.0003</v>
+        <v>-0.4855</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8211</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-9.3331</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>7.511699999999999</v>
+        <v>0.6828</v>
       </c>
       <c r="S9" t="n">
-        <v>2.513</v>
+        <v>0.1776</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8986</v>
+        <v>0.2319</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6145</v>
+        <v>-0.0544</v>
       </c>
       <c r="V9" t="n">
-        <v>-5.3609</v>
+        <v>-0.2667</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.4614</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.8995</v>
+        <v>-0.2667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>D. DREZNJAK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2409</v>
+        <v>-0.9853</v>
       </c>
       <c r="E10" t="n">
-        <v>14.7949</v>
+        <v>-0.3069</v>
       </c>
       <c r="F10" t="n">
-        <v>-19.0357</v>
+        <v>-0.6784</v>
       </c>
       <c r="G10" t="n">
-        <v>-15.8951</v>
+        <v>-0.7122000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-12.1578</v>
+        <v>0.9532</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7375</v>
+        <v>-1.6654</v>
       </c>
       <c r="J10" t="n">
-        <v>30.2178</v>
+        <v>0.5044</v>
       </c>
       <c r="K10" t="n">
-        <v>10.7428</v>
+        <v>1.4134</v>
       </c>
       <c r="L10" t="n">
-        <v>19.4747</v>
+        <v>-0.909</v>
       </c>
       <c r="M10" t="n">
-        <v>-46.1129</v>
+        <v>-1.2166</v>
       </c>
       <c r="N10" t="n">
-        <v>-22.9009</v>
+        <v>-0.4603</v>
       </c>
       <c r="O10" t="n">
-        <v>-23.2121</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.731299999999999</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-51.6721</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>48.9411</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-10.5822</v>
+        <v>-0.2731</v>
       </c>
       <c r="T10" t="n">
-        <v>-9.3653</v>
+        <v>0.1691</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2166</v>
+        <v>-0.4422</v>
       </c>
       <c r="V10" t="n">
-        <v>24.968</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>45.6148</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-20.6469</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.398</v>
+        <v>-3.7098</v>
       </c>
       <c r="E11" t="n">
-        <v>21.8877</v>
+        <v>-0.02600000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>-27.2853</v>
+        <v>-3.6841</v>
       </c>
       <c r="G11" t="n">
-        <v>-6.754400000000001</v>
+        <v>1.465500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-15.6383</v>
+        <v>2.7356</v>
       </c>
       <c r="I11" t="n">
-        <v>8.883199999999999</v>
+        <v>-1.2699</v>
       </c>
       <c r="J11" t="n">
-        <v>46.6252</v>
+        <v>9.4412</v>
       </c>
       <c r="K11" t="n">
-        <v>11.2123</v>
+        <v>5.7108</v>
       </c>
       <c r="L11" t="n">
-        <v>35.4135</v>
+        <v>3.7302</v>
       </c>
       <c r="M11" t="n">
-        <v>-53.3801</v>
+        <v>-7.9758</v>
       </c>
       <c r="N11" t="n">
-        <v>-26.85</v>
+        <v>-2.9753</v>
       </c>
       <c r="O11" t="n">
-        <v>-26.5303</v>
+        <v>-5.0003</v>
       </c>
       <c r="P11" t="n">
-        <v>17.528</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q11" t="n">
-        <v>-36.4212</v>
+        <v>-9.3331</v>
       </c>
       <c r="R11" t="n">
-        <v>53.9492</v>
+        <v>7.511699999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>-14.997</v>
+        <v>2.0069</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.0392</v>
+        <v>1.3273</v>
       </c>
       <c r="U11" t="n">
-        <v>-11.9577</v>
+        <v>0.6796</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.173</v>
+        <v>-5.3609</v>
       </c>
       <c r="W11" t="n">
-        <v>14.7231</v>
+        <v>-1.4614</v>
       </c>
       <c r="X11" t="n">
-        <v>-15.896</v>
+        <v>-3.8995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. APIC</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.907400000000001</v>
+        <v>-5.5447</v>
       </c>
       <c r="E12" t="n">
-        <v>5.701000000000001</v>
+        <v>15.5155</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.6087</v>
+        <v>-21.0603</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.3598</v>
+        <v>-3.402000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9623999999999999</v>
+        <v>4.071</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3975</v>
+        <v>-7.473100000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>17.7756</v>
+        <v>29.1501</v>
       </c>
       <c r="K12" t="n">
-        <v>12.4214</v>
+        <v>20.3994</v>
       </c>
       <c r="L12" t="n">
-        <v>5.3544</v>
+        <v>8.750400000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.1353</v>
+        <v>-32.5522</v>
       </c>
       <c r="N12" t="n">
-        <v>-13.3834</v>
+        <v>-16.3285</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.751899999999999</v>
+        <v>-16.224</v>
       </c>
       <c r="P12" t="n">
-        <v>4.5527</v>
+        <v>-0.2275999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-25.7227</v>
+        <v>-33.6897</v>
       </c>
       <c r="R12" t="n">
-        <v>30.2752</v>
+        <v>33.4622</v>
       </c>
       <c r="S12" t="n">
-        <v>4.872100000000001</v>
+        <v>9.1976</v>
       </c>
       <c r="T12" t="n">
-        <v>8.1411</v>
+        <v>9.3598</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.2691</v>
+        <v>-0.1619000000000003</v>
       </c>
       <c r="V12" t="n">
-        <v>-12.9724</v>
+        <v>-11.1125</v>
       </c>
       <c r="W12" t="n">
-        <v>5.5072</v>
+        <v>10.6952</v>
       </c>
       <c r="X12" t="n">
-        <v>-18.4794</v>
+        <v>-21.8077</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. MAVRA</t>
+          <t>J. WALKER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.1928</v>
+        <v>-13.0664</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.090899999999999</v>
+        <v>-4.297800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.102</v>
+        <v>-8.7684</v>
       </c>
       <c r="G13" t="n">
-        <v>37.5372</v>
+        <v>-3.1783</v>
       </c>
       <c r="H13" t="n">
-        <v>17.0981</v>
+        <v>-2.1229</v>
       </c>
       <c r="I13" t="n">
-        <v>20.4395</v>
+        <v>-1.0553</v>
       </c>
       <c r="J13" t="n">
-        <v>71.63590000000001</v>
+        <v>0.9037000000000003</v>
       </c>
       <c r="K13" t="n">
-        <v>34.9571</v>
+        <v>-0.1972</v>
       </c>
       <c r="L13" t="n">
-        <v>36.6795</v>
+        <v>1.1007</v>
       </c>
       <c r="M13" t="n">
-        <v>-34.0986</v>
+        <v>-4.0818</v>
       </c>
       <c r="N13" t="n">
-        <v>-17.8589</v>
+        <v>-1.9258</v>
       </c>
       <c r="O13" t="n">
-        <v>-16.2398</v>
+        <v>-2.156</v>
       </c>
       <c r="P13" t="n">
-        <v>-49.1684</v>
+        <v>-4.3251</v>
       </c>
       <c r="Q13" t="n">
-        <v>-97.1985</v>
+        <v>-5.9184</v>
       </c>
       <c r="R13" t="n">
-        <v>48.0305</v>
+        <v>1.5935</v>
       </c>
       <c r="S13" t="n">
-        <v>-13.1915</v>
+        <v>-0.7806000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.8203</v>
+        <v>0.7170000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-10.3706</v>
+        <v>-1.4976</v>
       </c>
       <c r="V13" t="n">
-        <v>13.6298</v>
+        <v>-4.7823</v>
       </c>
       <c r="W13" t="n">
-        <v>22.2927</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.662799999999999</v>
+        <v>-4.7823</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. WALKER</t>
+          <t>D. APIC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.316</v>
+        <v>-13.7252</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.7926</v>
+        <v>-0.1862999999999997</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.523399999999999</v>
+        <v>-13.5392</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.1783</v>
+        <v>-4.3598</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.1229</v>
+        <v>-0.9623999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0553</v>
+        <v>-3.3975</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9037000000000003</v>
+        <v>17.7756</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1972</v>
+        <v>12.4214</v>
       </c>
       <c r="L14" t="n">
-        <v>1.1007</v>
+        <v>5.3544</v>
       </c>
       <c r="M14" t="n">
-        <v>-4.0818</v>
+        <v>-22.1353</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.9258</v>
+        <v>-13.3834</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.156</v>
+        <v>-8.751899999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-4.3251</v>
+        <v>4.5527</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.9184</v>
+        <v>-25.7227</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5935</v>
+        <v>30.2752</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0303</v>
+        <v>-0.9456</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2222</v>
+        <v>2.2537</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.2526</v>
+        <v>-3.1991</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.7823</v>
+        <v>-12.9724</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>5.5072</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.7823</v>
+        <v>-18.4794</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>-57.6832</v>
+        <v>-37.4904</v>
       </c>
       <c r="E15" t="n">
-        <v>-23.674</v>
+        <v>-10.4912</v>
       </c>
       <c r="F15" t="n">
-        <v>-34.0094</v>
+        <v>-26.9993</v>
       </c>
       <c r="G15" t="n">
         <v>8.856399999999999</v>
@@ -1624,13 +1624,13 @@
         <v>56.6803</v>
       </c>
       <c r="S15" t="n">
-        <v>-29.0241</v>
+        <v>-8.831100000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-12.2222</v>
+        <v>0.9603999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-16.8014</v>
+        <v>-9.791399999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-12.2486</v>
@@ -1657,13 +1657,13 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>-62.4041</v>
+        <v>-47.1102</v>
       </c>
       <c r="E16" t="n">
-        <v>-42.088</v>
+        <v>-31.9847</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.3164</v>
+        <v>-15.1255</v>
       </c>
       <c r="G16" t="n">
         <v>-54.9498</v>
@@ -1702,13 +1702,13 @@
         <v>57.5909</v>
       </c>
       <c r="S16" t="n">
-        <v>-21.103</v>
+        <v>-5.809299999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-8.414400000000001</v>
+        <v>1.6886</v>
       </c>
       <c r="U16" t="n">
-        <v>-12.6887</v>
+        <v>-7.4978</v>
       </c>
       <c r="V16" t="n">
         <v>-10.2524</v>
@@ -1735,16 +1735,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>-56.70709999999998</v>
+        <v>-25.8831</v>
       </c>
       <c r="E17" t="n">
-        <v>137.6136</v>
+        <v>146.327</v>
       </c>
       <c r="F17" t="n">
-        <v>-194.3212</v>
+        <v>-172.2112</v>
       </c>
       <c r="G17" t="n">
-        <v>-81.57069999999999</v>
+        <v>-81.5707</v>
       </c>
       <c r="H17" t="n">
         <v>-50.8255</v>
@@ -1753,7 +1753,7 @@
         <v>-30.74619999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>371.4807000000001</v>
+        <v>371.4807</v>
       </c>
       <c r="K17" t="n">
         <v>168.8523</v>
@@ -1777,19 +1777,19 @@
         <v>-525.8306</v>
       </c>
       <c r="R17" t="n">
-        <v>563.3903</v>
+        <v>563.3902999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-18.23700000000001</v>
+        <v>12.5857</v>
       </c>
       <c r="T17" t="n">
-        <v>47.8235</v>
+        <v>56.5353</v>
       </c>
       <c r="U17" t="n">
-        <v>-66.0599</v>
+        <v>-43.9492</v>
       </c>
       <c r="V17" t="n">
-        <v>5.543499999999993</v>
+        <v>5.5435</v>
       </c>
       <c r="W17" t="n">
         <v>244.1414</v>
